--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124189908</v>
+        <v>124190114</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,16 +718,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660965</v>
+        <v>660961</v>
       </c>
       <c r="R2" t="n">
-        <v>6555755</v>
+        <v>6555751</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vildsvinsbök</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124188664</v>
+        <v>124189908</v>
       </c>
       <c r="B3" t="n">
-        <v>103528</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,38 +818,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660948</v>
+        <v>660965</v>
       </c>
       <c r="R3" t="n">
-        <v>6555846</v>
+        <v>6555755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vildsvinsbök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1135,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124190114</v>
+        <v>124188664</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>103528</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,52 +1166,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogshyddan, Skogshyddan, Srm</t>
+          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660961</v>
+        <v>660948</v>
       </c>
       <c r="R6" t="n">
-        <v>6555751</v>
+        <v>6555846</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,12 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124554673</v>
+        <v>124554169</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,35 +1278,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660898</v>
+        <v>661003</v>
       </c>
       <c r="R7" t="n">
-        <v>6555753</v>
+        <v>6555739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1365,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554169</v>
+        <v>124554673</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,40 +1409,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1441,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661003</v>
+        <v>660898</v>
       </c>
       <c r="R8" t="n">
-        <v>6555739</v>
+        <v>6555753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124190114</v>
+        <v>124189908</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,21 +718,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660961</v>
+        <v>660965</v>
       </c>
       <c r="R2" t="n">
-        <v>6555751</v>
+        <v>6555755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>Vildsvinsbök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124189908</v>
+        <v>124190114</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -841,7 +836,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,16 +844,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660965</v>
+        <v>660961</v>
       </c>
       <c r="R3" t="n">
-        <v>6555755</v>
+        <v>6555751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vildsvinsbök</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1042,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124189238</v>
+        <v>124188664</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>103528</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,38 +1054,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogshyddan, Skogshyddan, Srm</t>
+          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660988</v>
+        <v>660948</v>
       </c>
       <c r="R5" t="n">
-        <v>6555758</v>
+        <v>6555846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124188664</v>
+        <v>124189238</v>
       </c>
       <c r="B6" t="n">
-        <v>103528</v>
+        <v>91032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,38 +1166,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660948</v>
+        <v>660988</v>
       </c>
       <c r="R6" t="n">
-        <v>6555846</v>
+        <v>6555758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124554169</v>
+        <v>124554673</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,40 +1278,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661003</v>
+        <v>660898</v>
       </c>
       <c r="R7" t="n">
-        <v>6555739</v>
+        <v>6555753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,12 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554673</v>
+        <v>124554169</v>
       </c>
       <c r="B8" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,35 +1399,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1446,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660898</v>
+        <v>661003</v>
       </c>
       <c r="R8" t="n">
-        <v>6555753</v>
+        <v>6555739</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124190114</v>
+        <v>124210054</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,52 +813,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogshyddan, Skogshyddan, Srm</t>
+          <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660961</v>
+        <v>660999</v>
       </c>
       <c r="R3" t="n">
-        <v>6555751</v>
+        <v>6555815</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,51 +881,37 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124210054</v>
+        <v>124189238</v>
       </c>
       <c r="B4" t="n">
         <v>91032</v>
@@ -965,24 +944,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660999</v>
+        <v>660988</v>
       </c>
       <c r="R4" t="n">
-        <v>6555815</v>
+        <v>6555758</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,30 +984,39 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1154,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189238</v>
+        <v>124190114</v>
       </c>
       <c r="B6" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,38 +1147,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660988</v>
+        <v>660961</v>
       </c>
       <c r="R6" t="n">
-        <v>6555758</v>
+        <v>6555751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1234,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124554673</v>
+        <v>124554169</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,35 +1278,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660898</v>
+        <v>661003</v>
       </c>
       <c r="R7" t="n">
-        <v>6555753</v>
+        <v>6555739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1365,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554169</v>
+        <v>124554220</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1422,7 +1432,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661003</v>
+        <v>660996</v>
       </c>
       <c r="R8" t="n">
-        <v>6555739</v>
+        <v>6555751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1518,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554220</v>
+        <v>124554673</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,40 +1540,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1572,10 +1577,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660996</v>
+        <v>660898</v>
       </c>
       <c r="R9" t="n">
-        <v>6555751</v>
+        <v>6555753</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1612,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,12 +1622,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124189908</v>
+        <v>124210054</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogshyddan, Skogshyddan, Srm</t>
+          <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660965</v>
+        <v>660999</v>
       </c>
       <c r="R2" t="n">
-        <v>6555755</v>
+        <v>6555815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,54 +755,40 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vildsvinsbök</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124210054</v>
+        <v>124190114</v>
       </c>
       <c r="B3" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,45 +797,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660999</v>
+        <v>660961</v>
       </c>
       <c r="R3" t="n">
-        <v>6555815</v>
+        <v>6555751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,30 +872,44 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1135,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124190114</v>
+        <v>124189908</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,7 +1175,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1178,21 +1183,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660961</v>
+        <v>660965</v>
       </c>
       <c r="R6" t="n">
-        <v>6555751</v>
+        <v>6555755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>Vildsvinsbök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554220</v>
+        <v>124554673</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,40 +1409,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1451,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660996</v>
+        <v>660898</v>
       </c>
       <c r="R8" t="n">
-        <v>6555751</v>
+        <v>6555753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,12 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554673</v>
+        <v>124554220</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,35 +1530,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1577,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660898</v>
+        <v>660996</v>
       </c>
       <c r="R9" t="n">
-        <v>6555753</v>
+        <v>6555751</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1612,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1622,7 +1617,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124210054</v>
+        <v>124188664</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>103528</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Srm</t>
+          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660999</v>
+        <v>660948</v>
       </c>
       <c r="R2" t="n">
-        <v>6555815</v>
+        <v>6555846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,37 +748,46 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124190114</v>
+        <v>124189908</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -820,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -828,21 +830,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660961</v>
+        <v>660965</v>
       </c>
       <c r="R3" t="n">
-        <v>6555751</v>
+        <v>6555755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,12 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>Vildsvinsbök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124189238</v>
+        <v>124210054</v>
       </c>
       <c r="B4" t="n">
         <v>91032</v>
@@ -949,17 +946,24 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogshyddan, Skogshyddan, Srm</t>
+          <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660988</v>
+        <v>660999</v>
       </c>
       <c r="R4" t="n">
-        <v>6555758</v>
+        <v>6555815</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,49 +993,40 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124188664</v>
+        <v>124189238</v>
       </c>
       <c r="B5" t="n">
-        <v>103528</v>
+        <v>91032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,38 +1035,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660948</v>
+        <v>660988</v>
       </c>
       <c r="R5" t="n">
-        <v>6555846</v>
+        <v>6555758</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189908</v>
+        <v>124190114</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1175,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1183,16 +1178,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660965</v>
+        <v>660961</v>
       </c>
       <c r="R6" t="n">
-        <v>6555755</v>
+        <v>6555751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vildsvinsbök</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554673</v>
+        <v>124554220</v>
       </c>
       <c r="B8" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,35 +1409,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1446,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660898</v>
+        <v>660996</v>
       </c>
       <c r="R8" t="n">
-        <v>6555753</v>
+        <v>6555751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1496,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554220</v>
+        <v>124554673</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,40 +1540,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1572,10 +1577,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660996</v>
+        <v>660898</v>
       </c>
       <c r="R9" t="n">
-        <v>6555751</v>
+        <v>6555753</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1612,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,12 +1622,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124188664</v>
+        <v>124190114</v>
       </c>
       <c r="B2" t="n">
-        <v>103528</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660948</v>
+        <v>660961</v>
       </c>
       <c r="R2" t="n">
-        <v>6555846</v>
+        <v>6555751</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1023,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124189238</v>
+        <v>124188664</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>103528</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,38 +1054,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogshyddan, Skogshyddan, Srm</t>
+          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660988</v>
+        <v>660948</v>
       </c>
       <c r="R5" t="n">
-        <v>6555758</v>
+        <v>6555846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124190114</v>
+        <v>124189238</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,52 +1166,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660961</v>
+        <v>660988</v>
       </c>
       <c r="R6" t="n">
-        <v>6555751</v>
+        <v>6555758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,12 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,7 +1266,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124554169</v>
+        <v>124554220</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661003</v>
+        <v>660996</v>
       </c>
       <c r="R7" t="n">
-        <v>6555739</v>
+        <v>6555751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554220</v>
+        <v>124554673</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,40 +1409,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1451,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660996</v>
+        <v>660898</v>
       </c>
       <c r="R8" t="n">
-        <v>6555751</v>
+        <v>6555753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,12 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554673</v>
+        <v>124554169</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,35 +1530,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1577,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660898</v>
+        <v>661003</v>
       </c>
       <c r="R9" t="n">
-        <v>6555753</v>
+        <v>6555739</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1612,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1622,7 +1617,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1042,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124188664</v>
+        <v>124189238</v>
       </c>
       <c r="B5" t="n">
-        <v>103528</v>
+        <v>91032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,38 +1054,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660948</v>
+        <v>660988</v>
       </c>
       <c r="R5" t="n">
-        <v>6555846</v>
+        <v>6555758</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189238</v>
+        <v>124188664</v>
       </c>
       <c r="B6" t="n">
-        <v>91032</v>
+        <v>103528</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,38 +1166,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogshyddan, Skogshyddan, Srm</t>
+          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660988</v>
+        <v>660948</v>
       </c>
       <c r="R6" t="n">
-        <v>6555758</v>
+        <v>6555846</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124554220</v>
+        <v>124554673</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,40 +1278,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660996</v>
+        <v>660898</v>
       </c>
       <c r="R7" t="n">
-        <v>6555751</v>
+        <v>6555753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,12 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554673</v>
+        <v>124554169</v>
       </c>
       <c r="B8" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,35 +1399,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1446,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660898</v>
+        <v>661003</v>
       </c>
       <c r="R8" t="n">
-        <v>6555753</v>
+        <v>6555739</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,7 +1518,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554169</v>
+        <v>124554220</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661003</v>
+        <v>660996</v>
       </c>
       <c r="R9" t="n">
-        <v>6555739</v>
+        <v>6555751</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124190114</v>
+        <v>124189238</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660961</v>
+        <v>660988</v>
       </c>
       <c r="R2" t="n">
-        <v>6555751</v>
+        <v>6555758</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124189908</v>
+        <v>124190114</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -841,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,16 +830,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660965</v>
+        <v>660961</v>
       </c>
       <c r="R3" t="n">
-        <v>6555755</v>
+        <v>6555751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vildsvinsbök</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1042,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124189238</v>
+        <v>124189908</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,38 +1040,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660988</v>
+        <v>660965</v>
       </c>
       <c r="R5" t="n">
-        <v>6555758</v>
+        <v>6555755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1122,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vildsvinsbök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554169</v>
+        <v>124554220</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661003</v>
+        <v>660996</v>
       </c>
       <c r="R8" t="n">
-        <v>6555739</v>
+        <v>6555751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1518,7 +1518,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554220</v>
+        <v>124554169</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660996</v>
+        <v>661003</v>
       </c>
       <c r="R9" t="n">
-        <v>6555751</v>
+        <v>6555739</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124189238</v>
+        <v>124188664</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>103528</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogshyddan, Skogshyddan, Srm</t>
+          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660988</v>
+        <v>660948</v>
       </c>
       <c r="R2" t="n">
-        <v>6555758</v>
+        <v>6555846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124190114</v>
+        <v>124210054</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,52 +799,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogshyddan, Skogshyddan, Srm</t>
+          <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660961</v>
+        <v>660999</v>
       </c>
       <c r="R3" t="n">
-        <v>6555751</v>
+        <v>6555815</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,54 +867,40 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124210054</v>
+        <v>124189908</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,45 +909,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660999</v>
+        <v>660965</v>
       </c>
       <c r="R4" t="n">
-        <v>6555815</v>
+        <v>6555755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,40 +979,54 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vildsvinsbök</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124189908</v>
+        <v>124189238</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,47 +1035,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660965</v>
+        <v>660988</v>
       </c>
       <c r="R5" t="n">
-        <v>6555755</v>
+        <v>6555758</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,12 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vildsvinsbök</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124188664</v>
+        <v>124190114</v>
       </c>
       <c r="B6" t="n">
-        <v>103528</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,38 +1147,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660948</v>
+        <v>660961</v>
       </c>
       <c r="R6" t="n">
-        <v>6555846</v>
+        <v>6555751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1234,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554220</v>
+        <v>124554169</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660996</v>
+        <v>661003</v>
       </c>
       <c r="R8" t="n">
-        <v>6555751</v>
+        <v>6555739</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1518,7 +1518,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554169</v>
+        <v>124554220</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661003</v>
+        <v>660996</v>
       </c>
       <c r="R9" t="n">
-        <v>6555739</v>
+        <v>6555751</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554169</v>
+        <v>124554220</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661003</v>
+        <v>660996</v>
       </c>
       <c r="R8" t="n">
-        <v>6555739</v>
+        <v>6555751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1518,7 +1518,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554220</v>
+        <v>124554169</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660996</v>
+        <v>661003</v>
       </c>
       <c r="R9" t="n">
-        <v>6555751</v>
+        <v>6555739</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1387,7 +1387,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554220</v>
+        <v>124554169</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660996</v>
+        <v>661003</v>
       </c>
       <c r="R8" t="n">
-        <v>6555751</v>
+        <v>6555739</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1518,7 +1518,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554169</v>
+        <v>124554220</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661003</v>
+        <v>660996</v>
       </c>
       <c r="R9" t="n">
-        <v>6555739</v>
+        <v>6555751</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124554673</v>
+        <v>124554220</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,35 +1278,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660898</v>
+        <v>660996</v>
       </c>
       <c r="R7" t="n">
-        <v>6555753</v>
+        <v>6555751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1365,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554169</v>
+        <v>124554673</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,40 +1409,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1441,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661003</v>
+        <v>660898</v>
       </c>
       <c r="R8" t="n">
-        <v>6555739</v>
+        <v>6555753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,7 +1518,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554220</v>
+        <v>124554169</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660996</v>
+        <v>661003</v>
       </c>
       <c r="R9" t="n">
-        <v>6555751</v>
+        <v>6555739</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1266,7 +1266,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124554220</v>
+        <v>124554169</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660996</v>
+        <v>661003</v>
       </c>
       <c r="R7" t="n">
-        <v>6555751</v>
+        <v>6555739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554673</v>
+        <v>124554220</v>
       </c>
       <c r="B8" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,35 +1409,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1446,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660898</v>
+        <v>660996</v>
       </c>
       <c r="R8" t="n">
-        <v>6555753</v>
+        <v>6555751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1496,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554169</v>
+        <v>124554673</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,40 +1540,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1572,10 +1577,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661003</v>
+        <v>660898</v>
       </c>
       <c r="R9" t="n">
-        <v>6555739</v>
+        <v>6555753</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1612,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,12 +1622,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124554169</v>
+        <v>124554673</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,40 +1278,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661003</v>
+        <v>660898</v>
       </c>
       <c r="R7" t="n">
-        <v>6555739</v>
+        <v>6555753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,12 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1528,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554673</v>
+        <v>124554169</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,35 +1530,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1577,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660898</v>
+        <v>661003</v>
       </c>
       <c r="R9" t="n">
-        <v>6555753</v>
+        <v>6555739</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1612,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1622,7 +1617,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1771,6 +1771,107 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131431501</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brink, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>661006</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6555744</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>131431501</v>
       </c>
       <c r="B11" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124188664</v>
+        <v>124189238</v>
       </c>
       <c r="B2" t="n">
-        <v>103528</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660948</v>
+        <v>660988</v>
       </c>
       <c r="R2" t="n">
-        <v>6555846</v>
+        <v>6555758</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +785,7 @@
         <v>124210054</v>
       </c>
       <c r="B3" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,47 +887,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124189908</v>
+        <v>124554673</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660965</v>
+        <v>660898</v>
       </c>
       <c r="R4" t="n">
-        <v>6555755</v>
+        <v>6555753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,27 +961,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vildsvinsbök</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1003,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124189238</v>
+        <v>124189908</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660988</v>
+        <v>660965</v>
       </c>
       <c r="R5" t="n">
-        <v>6555758</v>
+        <v>6555755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vildsvinsbök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,12 +1127,7 @@
         <v>124190114</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,47 +1250,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124554673</v>
+        <v>124190261</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660898</v>
+        <v>660960</v>
       </c>
       <c r="R7" t="n">
-        <v>6555753</v>
+        <v>6555743</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,22 +1324,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,15 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124554220</v>
+        <v>124190539</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1396,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660996</v>
+        <v>660959</v>
       </c>
       <c r="R8" t="n">
-        <v>6555751</v>
+        <v>6555723</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,27 +1445,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>7 vinterståndare</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,15 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124554169</v>
+        <v>124193155</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1522,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1561,21 +1530,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661003</v>
+        <v>660936</v>
       </c>
       <c r="R9" t="n">
-        <v>6555739</v>
+        <v>6555729</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,27 +1566,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,15 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124554198</v>
+        <v>124553885</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1638,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1697,18 +1651,16 @@
           <t>vinterståndare</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661009</v>
+        <v>660993</v>
       </c>
       <c r="R10" t="n">
-        <v>6555746</v>
+        <v>6555719</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1738,14 +1690,24 @@
           <t>2025-04-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-29</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hittades av Gunilla på Byrsta kvarn.</t>
+          <t>Två vinterståndare</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,29 +1716,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131431501</v>
+        <v>124554009</v>
       </c>
       <c r="B11" t="n">
-        <v>99052</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,17 +1762,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brink, Srm</t>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661006</v>
+        <v>660993</v>
       </c>
       <c r="R11" t="n">
-        <v>6555744</v>
+        <v>6555724</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,12 +1813,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,19 +1848,1152 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124554122</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>660994</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6555735</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124554169</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>661003</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6555739</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124554198</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>661009</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6555746</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hittades av Gunilla på Byrsta kvarn.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124554220</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogshyddan, Skogshyddan, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>660996</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6555751</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131431501</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brink, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>661006</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6555744</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Karina Hälleberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124188664</v>
+      </c>
+      <c r="B17" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Byrsta kvarn, Byrsta kvarn, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>660948</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6555846</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124555298</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Kvarnbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>660831</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6555817</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124555344</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Kvarnbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>660850</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6555827</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124555403</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Kvarnbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>660873</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6555839</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124555317</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Kvarnbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>660839</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6555823</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14220-2025 artfynd.xlsx
+++ b/artfynd/A 14220-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124189238</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124210054</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124554673</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124189908</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124190114</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124190261</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,6 +1524,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124190539</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1605,6 +1645,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124193155</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1731,6 +1776,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553885</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1857,6 +1907,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124554009</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1973,6 +2028,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124554122</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2099,6 +2159,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124554169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2218,6 +2283,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124554198</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2344,6 +2414,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124554220</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2445,6 +2520,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431501</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2552,6 +2632,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124188664</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2659,6 +2744,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124555298</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2766,6 +2856,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124555344</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2887,6 +2982,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124555403</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2994,8 +3094,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124555317</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>